--- a/11-CollaborationList/InstituteCancerResearch.xlsx
+++ b/11-CollaborationList/InstituteCancerResearch.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2050112097543/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{869C16E6-67EC-42F8-96C7-061E979DE185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DA041C7-FFAE-8D47-8593-2CE0F4F251BF}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{869C16E6-67EC-42F8-96C7-061E979DE185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0FFBB65-F2BF-C447-939D-B6E6DDC13917}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" xr2:uid="{CC4E119D-9618-D84F-B362-22684ABE43A6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>Title</t>
   </si>
@@ -98,9 +98,6 @@
     <t>ICR</t>
   </si>
   <si>
-    <t>The Institute of Cancer Research, 123 Old Brompton Road, London, SW7 3RP, UK</t>
-  </si>
-  <si>
     <t>0000-0001-9436-1832</t>
   </si>
   <si>
@@ -119,61 +116,6 @@
     <t>Emma J. Harris</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Joint </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Department of Physics, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Institute of Cancer Research </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">London, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>SM2 5NG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>, UK</t>
-    </r>
-  </si>
-  <si>
     <t>0000-0001-8297-0382</t>
   </si>
   <si>
@@ -201,18 +143,17 @@
     <t>J. C. Bamber</t>
   </si>
   <si>
-    <t>Joint Department of Physics, Institute of Cancer Research and Royal Marsden NHS Foundation Trust, Sir Richard Doll Building
-28 Oakleaf Avenue, Sutton, London, SM2 5GP</t>
-  </si>
-  <si>
     <t>jeff.bamber@icr.ac.uk; jeff@icr.ac.uk; jeffrey.bamber@icr.ac.uk</t>
+  </si>
+  <si>
+    <t>Joint Department of Physics, Institute of Cancer Research and Royal Marsden NHS Foundation Trust, Sir Richard Doll Building, 28 Oakleaf Avenue, Sutton, London, SM2 5GP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -235,20 +176,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -338,7 +265,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -757,16 +684,16 @@
         <v>18</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I2" s="4">
         <v>0</v>
@@ -776,36 +703,36 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="31" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>27</v>
+      <c r="H3" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="I3" s="6">
         <v>0</v>
@@ -815,36 +742,36 @@
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
